--- a/regist_complete.php 単体テスト仕様書.xlsx
+++ b/regist_complete.php 単体テスト仕様書.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
   <si>
     <t>テスト区分</t>
   </si>
@@ -56,6 +56,18 @@
   </si>
   <si>
     <t>画面中央に正しく表示される</t>
+  </si>
+  <si>
+    <t>NG</t>
+  </si>
+  <si>
+    <t>早川</t>
+  </si>
+  <si>
+    <t>画面の左端に「登録完了しました」が表示された</t>
+  </si>
+  <si>
+    <t>PC/ブラウザ</t>
   </si>
   <si>
     <t>ボタン表示</t>
@@ -72,6 +84,9 @@
   </si>
   <si>
     <t>ボタンが表示されている</t>
+  </si>
+  <si>
+    <t>OK</t>
   </si>
   <si>
     <t>TOP遷移</t>
@@ -133,9 +148,6 @@
     <t>再登録処理が行われない</t>
   </si>
   <si>
-    <t>二重登録が発生しない</t>
-  </si>
-  <si>
     <t>画面表示</t>
   </si>
   <si>
@@ -154,7 +166,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d"/>
+  </numFmts>
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -170,10 +185,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -210,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -227,11 +238,14 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -453,6 +467,7 @@
     <col customWidth="1" min="3" max="3" width="29.25"/>
     <col customWidth="1" min="4" max="4" width="46.5"/>
     <col customWidth="1" min="5" max="5" width="29.5"/>
+    <col customWidth="1" min="9" max="9" width="41.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -501,11 +516,21 @@
       <c r="E2" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="5"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
+      <c r="F2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="6">
+        <v>46105.0</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4"/>
@@ -513,19 +538,27 @@
         <v>2.0</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
+      <c r="H3" s="6">
+        <v>46105.0</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4"/>
@@ -533,19 +566,27 @@
         <v>3.0</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="6">
+        <v>46105.0</v>
+      </c>
+      <c r="I4" s="8"/>
+      <c r="J4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
     </row>
     <row r="5">
       <c r="A5" s="4"/>
@@ -553,19 +594,27 @@
         <v>4.0</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
+      <c r="G5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="6">
+        <v>46105.0</v>
+      </c>
+      <c r="I5" s="8"/>
+      <c r="J5" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4"/>
@@ -573,19 +622,27 @@
         <v>5.0</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="6">
+        <v>46105.0</v>
+      </c>
+      <c r="I6" s="8"/>
+      <c r="J6" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4"/>
@@ -593,19 +650,27 @@
         <v>6.0</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="6">
+        <v>46105.0</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="J7" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4"/>
@@ -613,43 +678,31 @@
         <v>7.0</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="5"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5">
-        <v>8.0</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="5"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
+        <v>34</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="6">
+        <v>46105.0</v>
+      </c>
+      <c r="I8" s="8"/>
+      <c r="J8" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:G4 H7:H8 F5:F9">
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="F2:F8">
       <formula1>"OK,NG"</formula1>
     </dataValidation>
   </dataValidations>

--- a/regist_complete.php 単体テスト仕様書.xlsx
+++ b/regist_complete.php 単体テスト仕様書.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="33">
   <si>
     <t>テスト区分</t>
   </si>
@@ -58,13 +58,10 @@
     <t>画面中央に正しく表示される</t>
   </si>
   <si>
-    <t>NG</t>
+    <t>OK</t>
   </si>
   <si>
     <t>早川</t>
-  </si>
-  <si>
-    <t>画面の左端に「登録完了しました」が表示された</t>
   </si>
   <si>
     <t>PC/ブラウザ</t>
@@ -84,9 +81,6 @@
   </si>
   <si>
     <t>ボタンが表示されている</t>
-  </si>
-  <si>
-    <t>OK</t>
   </si>
   <si>
     <t>TOP遷移</t>
@@ -525,11 +519,9 @@
       <c r="H2" s="6">
         <v>46105.0</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="7"/>
+      <c r="J2" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -538,26 +530,26 @@
         <v>2.0</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="E3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H3" s="6">
-        <v>46105.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I3" s="8"/>
       <c r="J3" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -566,26 +558,26 @@
         <v>3.0</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H4" s="6">
-        <v>46105.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I4" s="8"/>
       <c r="J4" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -594,26 +586,26 @@
         <v>4.0</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="F5" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H5" s="6">
-        <v>46105.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I5" s="8"/>
       <c r="J5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -622,26 +614,26 @@
         <v>5.0</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="6">
-        <v>46105.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I6" s="8"/>
       <c r="J6" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -650,26 +642,26 @@
         <v>6.0</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G7" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="6">
-        <v>46105.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I7" s="8"/>
       <c r="J7" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -678,26 +670,26 @@
         <v>7.0</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>14</v>
       </c>
       <c r="H8" s="6">
-        <v>46105.0</v>
+        <v>46112.0</v>
       </c>
       <c r="I8" s="8"/>
       <c r="J8" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
